--- a/data/trans_dic/IP25A_R_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R_2023-Clase-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 26,0</t>
+          <t>7,33; 18,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 17,4</t>
+          <t>7,6; 19,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 18,13</t>
+          <t>8,81; 16,49</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 21,46</t>
+          <t>11,57; 26,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,61; 26,09</t>
+          <t>9,23; 21,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 21,65</t>
+          <t>11,76; 21,9</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 20,68</t>
+          <t>6,65; 22,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 22,08</t>
+          <t>6,0; 21,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 18,56</t>
+          <t>8,13; 18,95</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 14,63</t>
+          <t>10,01; 19,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 19,03</t>
+          <t>8,95; 17,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 14,84</t>
+          <t>10,5; 16,44</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 27,38</t>
+          <t>7,27; 17,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,88</t>
+          <t>11,22; 22,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,58; 19,3</t>
+          <t>10,35; 17,83</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 26,76</t>
+          <t>6,44; 22,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 21,84</t>
+          <t>7,55; 21,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,35</t>
+          <t>8,78; 19,15</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,24; 16,81</t>
+          <t>11,17; 15,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,29; 16,15</t>
+          <t>11,5; 16,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,01; 15,55</t>
+          <t>11,96; 15,48</t>
         </is>
       </c>
     </row>
@@ -927,18 +927,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 98,91%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15139</t>
+          <t>14982</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16013</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>27629</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9434; 26312</t>
+          <t>8959; 22718</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9953; 23752</t>
+          <t>7592; 19231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22105; 43097</t>
+          <t>19562; 36611</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17504</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>30051</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8491; 19906</t>
+          <t>10578; 23865</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11099; 24935</t>
+          <t>8740; 20480</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22767; 40773</t>
+          <t>21898; 40759</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>14039</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2989; 10723</t>
+          <t>3788; 12592</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4782; 14097</t>
+          <t>3210; 11574</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9260; 21481</t>
+          <t>8979; 20928</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52638</t>
+          <t>50280</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13719; 31594</t>
+          <t>20174; 39809</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21485; 41418</t>
+          <t>15821; 30324</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39413; 64363</t>
+          <t>39687; 62174</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>21399</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41092</t>
+          <t>36097</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14421; 32013</t>
+          <t>10750; 25570</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13182; 29014</t>
+          <t>13038; 26192</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29524; 53875</t>
+          <t>27339; 47095</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8651</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>18058</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6207; 18040</t>
+          <t>4278; 14818</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4661; 15324</t>
+          <t>5220; 14765</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12955; 29364</t>
+          <t>11903; 25976</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>89351</t>
+          <t>92556</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>100690</t>
+          <t>83598</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190041</t>
+          <t>176154</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>72610; 108616</t>
+          <t>76651; 108908</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>84205; 120506</t>
+          <t>70179; 98040</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>167230; 216477</t>
+          <t>155086; 200710</t>
         </is>
       </c>
     </row>
